--- a/Output Coni/params_2k1b_all_families.xlsx
+++ b/Output Coni/params_2k1b_all_families.xlsx
@@ -108,14 +108,14 @@
     <col min="3" max="3" width="14.21875" customWidth="true"/>
     <col min="4" max="4" width="15.21875" customWidth="true"/>
     <col min="5" max="5" width="15.21875" customWidth="true"/>
-    <col min="6" max="6" width="14.21875" customWidth="true"/>
-    <col min="7" max="7" width="14.21875" customWidth="true"/>
-    <col min="8" max="8" width="16.21875" customWidth="true"/>
-    <col min="9" max="9" width="15.5546875" customWidth="true"/>
-    <col min="10" max="10" width="13.5546875" customWidth="true"/>
-    <col min="11" max="11" width="14.21875" customWidth="true"/>
-    <col min="12" max="12" width="14.21875" customWidth="true"/>
-    <col min="13" max="13" width="14.5546875" customWidth="true"/>
+    <col min="6" max="6" width="13.6640625" customWidth="true"/>
+    <col min="7" max="7" width="15.21875" customWidth="true"/>
+    <col min="8" max="8" width="15.5546875" customWidth="true"/>
+    <col min="9" max="9" width="14.21875" customWidth="true"/>
+    <col min="10" max="10" width="15.21875" customWidth="true"/>
+    <col min="11" max="11" width="13.21875" customWidth="true"/>
+    <col min="12" max="12" width="13.21875" customWidth="true"/>
+    <col min="13" max="13" width="13.5546875" customWidth="true"/>
     <col min="14" max="14" width="5.6640625" customWidth="true"/>
   </cols>
   <sheetData>
@@ -168,40 +168,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C2" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D2" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E2" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F2" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G2" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H2" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I2" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J2" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K2" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L2" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M2" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N2" s="0">
         <v>1</v>
@@ -212,40 +212,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C3" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D3" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E3" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F3" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G3" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H3" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I3" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J3" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K3" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L3" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M3" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N3" s="0">
         <v>1</v>
@@ -256,40 +256,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>5.1703465592204001e-08</v>
+        <v>5.1038713572317599e-08</v>
       </c>
       <c r="C4" s="0">
-        <v>0.25934041761617799</v>
+        <v>0.69652352865812195</v>
       </c>
       <c r="D4" s="0">
-        <v>0.67399646114548095</v>
+        <v>0.673996508607839</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.23441717797122399</v>
+        <v>7.6556765511177395e-07</v>
       </c>
       <c r="F4" s="0">
-        <v>-0.108183802437075</v>
+        <v>0.70137472828388303</v>
       </c>
       <c r="G4" s="0">
-        <v>0.57480704977466301</v>
+        <v>0.67399668212803598</v>
       </c>
       <c r="H4" s="0">
-        <v>-0.0672034616089493</v>
+        <v>7.6556479564345505e-07</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.389886998502944</v>
+        <v>0.64711514248714996</v>
       </c>
       <c r="J4" s="0">
-        <v>0.57797516090010503</v>
+        <v>0.67399735317548604</v>
       </c>
       <c r="K4" s="0">
-        <v>-0.25934036591271242</v>
+        <v>-0.69652347761940836</v>
       </c>
       <c r="L4" s="0">
-        <v>-0.12623337553414898</v>
+        <v>-0.70137396271622787</v>
       </c>
       <c r="M4" s="0">
-        <v>0.3226835368939947</v>
+        <v>-0.6471143769223543</v>
       </c>
       <c r="N4" s="0">
         <v>1</v>
@@ -300,40 +300,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>1.4653735275241801e-09</v>
+        <v>2.9640046770276401e-08</v>
       </c>
       <c r="C5" s="0">
-        <v>0.251323159037182</v>
+        <v>0.67351438106308004</v>
       </c>
       <c r="D5" s="0">
-        <v>1.2487143858769201</v>
+        <v>1.2487145120752201</v>
       </c>
       <c r="E5" s="0">
-        <v>-0.20283963585956799</v>
+        <v>1.60872602333969e-07</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.41325289838489299</v>
+        <v>0.64354909802126203</v>
       </c>
       <c r="G5" s="0">
-        <v>1.0850815868874899</v>
+        <v>1.2487146467633801</v>
       </c>
       <c r="H5" s="0">
-        <v>0.018490183874122601</v>
+        <v>0.018485976741730002</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.8027933501719999</v>
+        <v>0.77304905804394097</v>
       </c>
       <c r="J5" s="0">
-        <v>1.2987574892962399</v>
+        <v>1.2987452573349001</v>
       </c>
       <c r="K5" s="0">
-        <v>-0.25132315757180845</v>
+        <v>-0.67351435142303329</v>
       </c>
       <c r="L5" s="0">
-        <v>0.210413262525325</v>
+        <v>-0.64354893714865968</v>
       </c>
       <c r="M5" s="0">
-        <v>1.8212835340461226</v>
+        <v>-0.75456308130221095</v>
       </c>
       <c r="N5" s="0">
         <v>1</v>
@@ -344,40 +344,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C6" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D6" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E6" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F6" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G6" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H6" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I6" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J6" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K6" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L6" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M6" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N6" s="0">
         <v>1</v>
@@ -388,40 +388,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C7" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D7" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E7" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F7" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G7" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H7" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I7" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J7" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K7" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L7" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M7" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N7" s="0">
         <v>1</v>
@@ -432,40 +432,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C8" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D8" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E8" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F8" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G8" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H8" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I8" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J8" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K8" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L8" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M8" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N8" s="0">
         <v>1</v>
@@ -476,40 +476,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>1.04638226871992e-08</v>
+        <v>1.04639049951216e-08</v>
       </c>
       <c r="C9" s="0">
-        <v>0.25198340973150701</v>
+        <v>0.67450955351980502</v>
       </c>
       <c r="D9" s="0">
-        <v>1.39990522829329</v>
+        <v>1.3999049692738199</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.30678351189601499</v>
+        <v>2.01126747883495e-07</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.179628477557154</v>
+        <v>0.63032124088415498</v>
       </c>
       <c r="G9" s="0">
-        <v>1.15549041831101</v>
+        <v>1.39990560547878</v>
       </c>
       <c r="H9" s="0">
-        <v>-0.115811528186041</v>
+        <v>2.6687498161483599e-07</v>
       </c>
       <c r="I9" s="0">
-        <v>-2.0056124013480701</v>
+        <v>0.68469111394718196</v>
       </c>
       <c r="J9" s="0">
-        <v>1.0711668355344699</v>
+        <v>1.39990598980995</v>
       </c>
       <c r="K9" s="0">
-        <v>-0.25198339926768432</v>
+        <v>-0.67450954305590005</v>
       </c>
       <c r="L9" s="0">
-        <v>-0.12715503433886099</v>
+        <v>-0.63032103975740705</v>
       </c>
       <c r="M9" s="0">
-        <v>1.889800873162029</v>
+        <v>-0.68469084707220029</v>
       </c>
       <c r="N9" s="0">
         <v>1</v>
@@ -520,40 +520,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>7.3284547499914598e-07</v>
+        <v>7.3292095485050402e-09</v>
       </c>
       <c r="C10" s="0">
-        <v>0.25056715399219598</v>
+        <v>0.72030491973085198</v>
       </c>
       <c r="D10" s="0">
-        <v>1.83421941864897</v>
+        <v>1.8342156209184599</v>
       </c>
       <c r="E10" s="0">
-        <v>-0.42986725620246602</v>
+        <v>1.191813854087e-07</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.46207385968933501</v>
+        <v>0.67070917600260704</v>
       </c>
       <c r="G10" s="0">
-        <v>1.4597487175605099</v>
+        <v>1.8342147389594501</v>
       </c>
       <c r="H10" s="0">
-        <v>-0.167840607093004</v>
+        <v>9.9104467361059598e-08</v>
       </c>
       <c r="I10" s="0">
-        <v>-1.64477718253543</v>
+        <v>0.69007237675181898</v>
       </c>
       <c r="J10" s="0">
-        <v>1.3758881660973501</v>
+        <v>1.8342160365439899</v>
       </c>
       <c r="K10" s="0">
-        <v>-0.25056642114672095</v>
+        <v>-0.72030491240164241</v>
       </c>
       <c r="L10" s="0">
-        <v>0.03220660348686899</v>
+        <v>-0.67070905682122162</v>
       </c>
       <c r="M10" s="0">
-        <v>1.476936575442426</v>
+        <v>-0.69007227764735157</v>
       </c>
       <c r="N10" s="0">
         <v>1</v>
@@ -564,40 +564,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>0.062427433286232202</v>
+        <v>0.062427418340794301</v>
       </c>
       <c r="C11" s="0">
-        <v>0.25000239716085698</v>
+        <v>0.74542644218596799</v>
       </c>
       <c r="D11" s="0">
-        <v>12.8146849915556</v>
+        <v>12.8143690370068</v>
       </c>
       <c r="E11" s="0">
-        <v>0.228056528831377</v>
+        <v>0.22805661945605901</v>
       </c>
       <c r="F11" s="0">
-        <v>-1.3707119878954599</v>
+        <v>0.76830158975243501</v>
       </c>
       <c r="G11" s="0">
-        <v>6.7322315622314202</v>
+        <v>6.7322456971259097</v>
       </c>
       <c r="H11" s="0">
-        <v>0.211319347629778</v>
+        <v>0.21131941417552799</v>
       </c>
       <c r="I11" s="0">
-        <v>-16.900193038257001</v>
+        <v>0.75019926270383597</v>
       </c>
       <c r="J11" s="0">
-        <v>9.2402070080104703</v>
+        <v>9.2401896822037308</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.18757496387462477</v>
+        <v>-0.68299902384517364</v>
       </c>
       <c r="L11" s="0">
-        <v>1.5987685167268368</v>
+        <v>-0.54024497029637597</v>
       </c>
       <c r="M11" s="0">
-        <v>17.11151238588678</v>
+        <v>-0.53887984852830795</v>
       </c>
       <c r="N11" s="0">
         <v>1</v>
@@ -608,40 +608,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>0.017295276007759</v>
+        <v>0.0172952782488957</v>
       </c>
       <c r="C12" s="0">
-        <v>0.24706929994254301</v>
+        <v>0.75013434800259204</v>
       </c>
       <c r="D12" s="0">
-        <v>1.17611377284443</v>
+        <v>1.17611381284516</v>
       </c>
       <c r="E12" s="0">
-        <v>-0.069171517506005697</v>
+        <v>1.9465647441131699e-07</v>
       </c>
       <c r="F12" s="0">
-        <v>0.35251486949112898</v>
+        <v>0.66884211411544903</v>
       </c>
       <c r="G12" s="0">
-        <v>1.0626147910501</v>
+        <v>1.12176907227976</v>
       </c>
       <c r="H12" s="0">
-        <v>-0.052429082591210402</v>
+        <v>5.4601166411303602e-08</v>
       </c>
       <c r="I12" s="0">
-        <v>-1.25902921274358</v>
+        <v>0.663142330551307</v>
       </c>
       <c r="J12" s="0">
-        <v>1.01166475254606</v>
+        <v>1.1217691216319099</v>
       </c>
       <c r="K12" s="0">
-        <v>-0.22977402393478402</v>
+        <v>-0.73283906975369639</v>
       </c>
       <c r="L12" s="0">
-        <v>-0.42168638699713468</v>
+        <v>-0.66884191945897464</v>
       </c>
       <c r="M12" s="0">
-        <v>1.2066001301523697</v>
+        <v>-0.66314227595014064</v>
       </c>
       <c r="N12" s="0">
         <v>1</v>
@@ -652,40 +652,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C13" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D13" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E13" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F13" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G13" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H13" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I13" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J13" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K13" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L13" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M13" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N13" s="0">
         <v>1</v>
@@ -696,40 +696,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C14" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D14" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E14" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F14" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G14" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H14" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I14" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J14" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K14" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L14" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M14" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N14" s="0">
         <v>1</v>
@@ -740,40 +740,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C15" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D15" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E15" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F15" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G15" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H15" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I15" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J15" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K15" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L15" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M15" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N15" s="0">
         <v>1</v>
@@ -784,40 +784,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>1.72431183743233e-07</v>
+        <v>6.9011172479228395e-07</v>
       </c>
       <c r="C16" s="0">
-        <v>0.25138932423765897</v>
+        <v>0.73957570924042204</v>
       </c>
       <c r="D16" s="0">
-        <v>0.54020187386963203</v>
+        <v>0.54020256521749099</v>
       </c>
       <c r="E16" s="0">
-        <v>-0.092389088863461796</v>
+        <v>5.1729463920685904e-07</v>
       </c>
       <c r="F16" s="0">
-        <v>-0.19687886878798799</v>
+        <v>0.73519322184352498</v>
       </c>
       <c r="G16" s="0">
-        <v>0.50484366762064503</v>
+        <v>0.54020189490327397</v>
       </c>
       <c r="H16" s="0">
-        <v>-0.071125472664384404</v>
+        <v>1.9138263082365099e-07</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.072426605819091994</v>
+        <v>0.71450103520677299</v>
       </c>
       <c r="J16" s="0">
-        <v>0.45821983900984897</v>
+        <v>0.54020191341879198</v>
       </c>
       <c r="K16" s="0">
-        <v>-0.25138915180647525</v>
+        <v>-0.73957501912869728</v>
       </c>
       <c r="L16" s="0">
-        <v>0.1044897799245262</v>
+        <v>-0.73519270454888574</v>
       </c>
       <c r="M16" s="0">
-        <v>0.0013011331547075899</v>
+        <v>-0.71450084382414214</v>
       </c>
       <c r="N16" s="0">
         <v>1</v>
@@ -828,40 +828,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1.6807836350311801e-07</v>
+        <v>1.6493070868187299e-07</v>
       </c>
       <c r="C17" s="0">
-        <v>0.24934680061556999</v>
+        <v>0.73721917574545104</v>
       </c>
       <c r="D17" s="0">
-        <v>0.20231009126716901</v>
+        <v>0.20230997271397</v>
       </c>
       <c r="E17" s="0">
-        <v>-1.0840939455420999</v>
+        <v>4.9479187720741601e-07</v>
       </c>
       <c r="F17" s="0">
-        <v>1.2295929391232301</v>
+        <v>0.75002465189528</v>
       </c>
       <c r="G17" s="0">
-        <v>0.11242180279235001</v>
+        <v>0.202310060180249</v>
       </c>
       <c r="H17" s="0">
-        <v>-0.19611679697426301</v>
+        <v>2.4719949142613501e-08</v>
       </c>
       <c r="I17" s="0">
-        <v>0.245911577369582</v>
+        <v>0.75684667693232999</v>
       </c>
       <c r="J17" s="0">
-        <v>0.11808152341005</v>
+        <v>0.20231001109522201</v>
       </c>
       <c r="K17" s="0">
-        <v>-0.24934663253720649</v>
+        <v>-0.73721901081474239</v>
       </c>
       <c r="L17" s="0">
-        <v>-2.31368688466533</v>
+        <v>-0.75002415710340276</v>
       </c>
       <c r="M17" s="0">
-        <v>-0.44202837434384501</v>
+        <v>-0.7568466522123809</v>
       </c>
       <c r="N17" s="0">
         <v>0</v>
@@ -872,40 +872,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C18" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D18" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E18" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F18" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G18" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H18" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I18" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J18" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K18" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L18" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M18" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N18" s="0">
         <v>0</v>
@@ -916,40 +916,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>0.032959995772887898</v>
+        <v>0.032959895458976998</v>
       </c>
       <c r="C19" s="0">
-        <v>0.249194520372299</v>
+        <v>0.74936280068464201</v>
       </c>
       <c r="D19" s="0">
-        <v>0.45460025583270403</v>
+        <v>0.45460009018068898</v>
       </c>
       <c r="E19" s="0">
-        <v>0.13556126859768999</v>
+        <v>0.13556170806016399</v>
       </c>
       <c r="F19" s="0">
-        <v>0.35684450765746001</v>
+        <v>0.68313902723117703</v>
       </c>
       <c r="G19" s="0">
-        <v>0.46906157271130999</v>
+        <v>0.46905708415706399</v>
       </c>
       <c r="H19" s="0">
-        <v>-0.084957041370757505</v>
+        <v>3.2138238451366302e-07</v>
       </c>
       <c r="I19" s="0">
-        <v>0.016729920926648</v>
+        <v>0.79026335280568905</v>
       </c>
       <c r="J19" s="0">
-        <v>0.33855997038590202</v>
+        <v>0.41961793218036503</v>
       </c>
       <c r="K19" s="0">
-        <v>-0.21623452459941112</v>
+        <v>-0.71640290522566497</v>
       </c>
       <c r="L19" s="0">
-        <v>-0.22128323905977001</v>
+        <v>-0.54757731917101304</v>
       </c>
       <c r="M19" s="0">
-        <v>-0.10168696229740551</v>
+        <v>-0.79026303142330456</v>
       </c>
       <c r="N19" s="0">
         <v>0</v>
@@ -960,40 +960,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>2.4507577503069501e-08</v>
+        <v>1.2256551687160799e-09</v>
       </c>
       <c r="C20" s="0">
-        <v>0.25554783324028202</v>
+        <v>0.68239258845763795</v>
       </c>
       <c r="D20" s="0">
-        <v>0.419617627020822</v>
+        <v>0.41961760636119</v>
       </c>
       <c r="E20" s="0">
-        <v>-2.4389911224634901</v>
+        <v>8.6927040947602699e-08</v>
       </c>
       <c r="F20" s="0">
-        <v>-1.0660252726044399</v>
+        <v>0.65662450012392803</v>
       </c>
       <c r="G20" s="0">
-        <v>0.16018981203718399</v>
+        <v>0.41961742606197799</v>
       </c>
       <c r="H20" s="0">
-        <v>-0.159039123381049</v>
+        <v>5.9704573800756299e-08</v>
       </c>
       <c r="I20" s="0">
-        <v>0.062083704588761099</v>
+        <v>0.68433599209466001</v>
       </c>
       <c r="J20" s="0">
-        <v>0.28995431917507403</v>
+        <v>0.419617963230702</v>
       </c>
       <c r="K20" s="0">
-        <v>-0.2555478087327045</v>
+        <v>-0.68239258723198282</v>
       </c>
       <c r="L20" s="0">
-        <v>-1.3729658498590502</v>
+        <v>-0.65662441319688714</v>
       </c>
       <c r="M20" s="0">
-        <v>-0.22112282796981009</v>
+        <v>-0.68433593239008617</v>
       </c>
       <c r="N20" s="0">
         <v>0</v>
@@ -1004,40 +1004,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>1.3720517940070101e-09</v>
+        <v>1.37199824337274e-07</v>
       </c>
       <c r="C21" s="0">
-        <v>0.23570438784490599</v>
+        <v>0.69596777561136802</v>
       </c>
       <c r="D21" s="0">
-        <v>0.67399643537929299</v>
+        <v>0.67399654525629804</v>
       </c>
       <c r="E21" s="0">
-        <v>-0.61308446036347597</v>
+        <v>7.5586310034242404e-08</v>
       </c>
       <c r="F21" s="0">
-        <v>0.67280798610463699</v>
+        <v>0.69507067313181303</v>
       </c>
       <c r="G21" s="0">
-        <v>0.475581716495384</v>
+        <v>0.673996577260217</v>
       </c>
       <c r="H21" s="0">
-        <v>-0.12831120196589099</v>
+        <v>1.99505504790114e-09</v>
       </c>
       <c r="I21" s="0">
-        <v>-0.18983909213067701</v>
+        <v>0.62864943827345299</v>
       </c>
       <c r="J21" s="0">
-        <v>0.51489669084248402</v>
+        <v>0.67399640233963498</v>
       </c>
       <c r="K21" s="0">
-        <v>-0.23570438647285419</v>
+        <v>-0.69596763841154363</v>
       </c>
       <c r="L21" s="0">
-        <v>-1.285892446468113</v>
+        <v>-0.69507059754550304</v>
       </c>
       <c r="M21" s="0">
-        <v>0.06152789016478602</v>
+        <v>-0.62864943627839798</v>
       </c>
       <c r="N21" s="0">
         <v>0</v>
@@ -1048,40 +1048,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>2.34790055479442e-08</v>
+        <v>2.3478827030530398e-08</v>
       </c>
       <c r="C22" s="0">
-        <v>0.249610645559082</v>
+        <v>0.607331265659663</v>
       </c>
       <c r="D22" s="0">
-        <v>0.47856247229360599</v>
+        <v>0.47856253148474698</v>
       </c>
       <c r="E22" s="0">
-        <v>-1.9590214853865699</v>
+        <v>7.4626288886234501e-08</v>
       </c>
       <c r="F22" s="0">
-        <v>-3.5105905018375498</v>
+        <v>0.65105412240650695</v>
       </c>
       <c r="G22" s="0">
-        <v>0.21010437707712001</v>
+        <v>0.47856252069073102</v>
       </c>
       <c r="H22" s="0">
-        <v>-0.20245302787640099</v>
+        <v>3.6415095329824001e-08</v>
       </c>
       <c r="I22" s="0">
-        <v>0.16291394017834401</v>
+        <v>0.69967565190749104</v>
       </c>
       <c r="J22" s="0">
-        <v>0.28937947583419799</v>
+        <v>0.47856253162597001</v>
       </c>
       <c r="K22" s="0">
-        <v>-0.24961062208007645</v>
+        <v>-0.60733124218083601</v>
       </c>
       <c r="L22" s="0">
-        <v>1.5515690164509799</v>
+        <v>-0.65105404778021803</v>
       </c>
       <c r="M22" s="0">
-        <v>-0.365366968054745</v>
+        <v>-0.69967561549239565</v>
       </c>
       <c r="N22" s="0">
         <v>0</v>
@@ -1092,40 +1092,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C23" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D23" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E23" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F23" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G23" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H23" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I23" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J23" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K23" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L23" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M23" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N23" s="0">
         <v>0</v>
@@ -1136,40 +1136,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>1.4388929514143e-07</v>
+        <v>1.43889449494597e-07</v>
       </c>
       <c r="C24" s="0">
-        <v>0.25116620878616502</v>
+        <v>0.70902018787058796</v>
       </c>
       <c r="D24" s="0">
-        <v>0.60511005613796398</v>
+        <v>0.60510988792328202</v>
       </c>
       <c r="E24" s="0">
-        <v>-0.65818643574634905</v>
+        <v>4.3166819814891001e-07</v>
       </c>
       <c r="F24" s="0">
-        <v>-2.9769778726712199</v>
+        <v>0.63327286799023996</v>
       </c>
       <c r="G24" s="0">
-        <v>0.41661945191123301</v>
+        <v>0.60510995817264801</v>
       </c>
       <c r="H24" s="0">
-        <v>-0.17881423071932601</v>
+        <v>3.9057034317986301e-08</v>
       </c>
       <c r="I24" s="0">
-        <v>0.044996567357742698</v>
+        <v>0.61491031255906103</v>
       </c>
       <c r="J24" s="0">
-        <v>0.37234612982508197</v>
+        <v>0.60510983584901001</v>
       </c>
       <c r="K24" s="0">
-        <v>-0.25116606489686988</v>
+        <v>-0.70902004398113849</v>
       </c>
       <c r="L24" s="0">
-        <v>2.318791436924871</v>
+        <v>-0.63327243632204178</v>
       </c>
       <c r="M24" s="0">
-        <v>-0.22381079807706872</v>
+        <v>-0.61491027350202676</v>
       </c>
       <c r="N24" s="0">
         <v>0</v>
@@ -1180,40 +1180,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>0.210050254624182</v>
+        <v>1.05708762903577</v>
       </c>
       <c r="C25" s="0">
-        <v>0.25001272998351198</v>
+        <v>0.714058153013165</v>
       </c>
       <c r="D25" s="0">
-        <v>1.1607509278673801e-06</v>
+        <v>2.7627911221562e-08</v>
       </c>
       <c r="E25" s="0">
-        <v>0.49965030633371599</v>
+        <v>0.63100142039645302</v>
       </c>
       <c r="F25" s="0">
-        <v>-0.27841292581129601</v>
+        <v>0.74975457567983606</v>
       </c>
       <c r="G25" s="0">
-        <v>-0.41711682308863601</v>
+        <v>5.7992760196018102e-06</v>
       </c>
       <c r="H25" s="0">
-        <v>1.0975661727577899</v>
+        <v>0.72428683559597395</v>
       </c>
       <c r="I25" s="0">
-        <v>1.45580874339723</v>
+        <v>0.74849985129293695</v>
       </c>
       <c r="J25" s="0">
-        <v>-0.61058555434508799</v>
+        <v>6.2797763768450794e-08</v>
       </c>
       <c r="K25" s="0">
-        <v>-0.03996247535932998</v>
+        <v>0.34302947602260503</v>
       </c>
       <c r="L25" s="0">
-        <v>0.77806323214501205</v>
+        <v>-0.11875315528338304</v>
       </c>
       <c r="M25" s="0">
-        <v>-0.35824257063944009</v>
+        <v>-0.024213015696962992</v>
       </c>
       <c r="N25" s="0">
         <v>0</v>
@@ -1224,40 +1224,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>0.0168321945375366</v>
+        <v>0.016832212709932799</v>
       </c>
       <c r="C26" s="0">
-        <v>0.250326230988618</v>
+        <v>0.72933890086562203</v>
       </c>
       <c r="D26" s="0">
-        <v>1.94007105926069</v>
+        <v>1.94007116578816</v>
       </c>
       <c r="E26" s="0">
-        <v>-0.035024676405690298</v>
+        <v>1.7413052385992799e-07</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.72382754575547703</v>
+        <v>0.66710832450706903</v>
       </c>
       <c r="G26" s="0">
-        <v>1.7767362689123101</v>
+        <v>1.83421597578455</v>
       </c>
       <c r="H26" s="0">
-        <v>0.066641979858002007</v>
+        <v>0.066641126548330307</v>
       </c>
       <c r="I26" s="0">
-        <v>-3.5117341492675802</v>
+        <v>0.74525947686629601</v>
       </c>
       <c r="J26" s="0">
-        <v>2.17955487049533</v>
+        <v>2.1795759737212999</v>
       </c>
       <c r="K26" s="0">
-        <v>-0.23349403645108141</v>
+        <v>-0.71250668815568918</v>
       </c>
       <c r="L26" s="0">
-        <v>0.68880286934978674</v>
+        <v>-0.66710815037654514</v>
       </c>
       <c r="M26" s="0">
-        <v>3.5783761291255822</v>
+        <v>-0.67861835031796569</v>
       </c>
       <c r="N26" s="0">
         <v>0</v>
@@ -1268,40 +1268,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>8.0150850666755996e-09</v>
+        <v>8.0149693373322702e-09</v>
       </c>
       <c r="C27" s="0">
-        <v>0.25208256112263899</v>
+        <v>0.74914909459788703</v>
       </c>
       <c r="D27" s="0">
-        <v>2.1928235672266601</v>
+        <v>2.1928237099594199</v>
       </c>
       <c r="E27" s="0">
-        <v>-0.20410392335489799</v>
+        <v>1.4583779736476999e-07</v>
       </c>
       <c r="F27" s="0">
-        <v>0.36270971395207302</v>
+        <v>0.73854979520388297</v>
       </c>
       <c r="G27" s="0">
-        <v>1.9008117795068</v>
+        <v>2.1928238794543802</v>
       </c>
       <c r="H27" s="0">
-        <v>-0.091098350599377306</v>
+        <v>1.9190580089386398e-09</v>
       </c>
       <c r="I27" s="0">
-        <v>-2.6982779502666001</v>
+        <v>0.75470809342909495</v>
       </c>
       <c r="J27" s="0">
-        <v>1.8200325297553499</v>
+        <v>2.1928236418676499</v>
       </c>
       <c r="K27" s="0">
-        <v>-0.25208255310755395</v>
+        <v>-0.74914908658291768</v>
       </c>
       <c r="L27" s="0">
-        <v>-0.56681363730697099</v>
+        <v>-0.73854964936608558</v>
       </c>
       <c r="M27" s="0">
-        <v>2.6071795996672229</v>
+        <v>-0.75470809151003693</v>
       </c>
       <c r="N27" s="0">
         <v>0</v>
@@ -1312,40 +1312,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C28" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D28" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E28" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F28" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G28" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H28" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I28" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J28" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K28" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L28" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M28" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N28" s="0">
         <v>0</v>
@@ -1356,40 +1356,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C29" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D29" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E29" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F29" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G29" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H29" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I29" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J29" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K29" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L29" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M29" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N29" s="0">
         <v>0</v>
@@ -1400,40 +1400,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>7.5017774819447799e-09</v>
+        <v>7.5011126400026196e-07</v>
       </c>
       <c r="C30" s="0">
-        <v>0.24997277607693599</v>
+        <v>0.704347385748608</v>
       </c>
       <c r="D30" s="0">
-        <v>1.5874010021219001</v>
+        <v>1.58740428144363</v>
       </c>
       <c r="E30" s="0">
-        <v>-0.69379156354917004</v>
+        <v>1.12509967794305e-09</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.27143228444015499</v>
+        <v>0.65768245625460697</v>
       </c>
       <c r="G30" s="0">
-        <v>1.1738552666409401</v>
+        <v>1.5874009632724699</v>
       </c>
       <c r="H30" s="0">
-        <v>-0.12503141524437</v>
+        <v>1.23576584608188e-09</v>
       </c>
       <c r="I30" s="0">
-        <v>-1.62713745380097</v>
+        <v>0.62227767223919905</v>
       </c>
       <c r="J30" s="0">
-        <v>1.2588920769730301</v>
+        <v>1.58740089689076</v>
       </c>
       <c r="K30" s="0">
-        <v>-0.24997276857515852</v>
+        <v>-0.70434663563734401</v>
       </c>
       <c r="L30" s="0">
-        <v>-0.42235927910901505</v>
+        <v>-0.65768245512950729</v>
       </c>
       <c r="M30" s="0">
-        <v>1.5021060385566001</v>
+        <v>-0.62227767100343323</v>
       </c>
       <c r="N30" s="0">
         <v>0</v>
@@ -1444,40 +1444,40 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>1.2515070737086999e-08</v>
+        <v>1.25140481581521e-08</v>
       </c>
       <c r="C31" s="0">
-        <v>0.25228783227995699</v>
+        <v>0.67295730548382005</v>
       </c>
       <c r="D31" s="0">
-        <v>1.1217690580703801</v>
+        <v>1.12176894909307</v>
       </c>
       <c r="E31" s="0">
-        <v>-0.486074181042502</v>
+        <v>2.0187162190128001e-07</v>
       </c>
       <c r="F31" s="0">
-        <v>-0.25138365271924201</v>
+        <v>0.58609921927315101</v>
       </c>
       <c r="G31" s="0">
-        <v>0.85544838691402902</v>
+        <v>1.12176891082578</v>
       </c>
       <c r="H31" s="0">
-        <v>-0.050068276341505097</v>
+        <v>9.9552102918602907e-08</v>
       </c>
       <c r="I31" s="0">
-        <v>-0.68205519135334902</v>
+        <v>0.67617672773353499</v>
       </c>
       <c r="J31" s="0">
-        <v>1.0079379390211201</v>
+        <v>1.1217690092138899</v>
       </c>
       <c r="K31" s="0">
-        <v>-0.25228781976488623</v>
+        <v>-0.67295729296977191</v>
       </c>
       <c r="L31" s="0">
-        <v>-0.23469052832325998</v>
+        <v>-0.58609901740152914</v>
       </c>
       <c r="M31" s="0">
-        <v>0.6319869150118439</v>
+        <v>-0.67617662818143209</v>
       </c>
       <c r="N31" s="0">
         <v>0</v>
@@ -1488,40 +1488,40 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0.104602132750527</v>
+        <v>0.104602128422879</v>
       </c>
       <c r="C32" s="0">
-        <v>0.249856754796626</v>
+        <v>0.73763091016192806</v>
       </c>
       <c r="D32" s="0">
-        <v>1.21360670811577</v>
+        <v>1.21360666446228</v>
       </c>
       <c r="E32" s="0">
-        <v>0.33288186393616997</v>
+        <v>0.33289246543536799</v>
       </c>
       <c r="F32" s="0">
-        <v>-0.401345686682755</v>
+        <v>0.71107756190590898</v>
       </c>
       <c r="G32" s="0">
-        <v>1.2162738117646399</v>
+        <v>1.2162783065440099</v>
       </c>
       <c r="H32" s="0">
-        <v>0.24492723579530901</v>
+        <v>0.244924796380593</v>
       </c>
       <c r="I32" s="0">
-        <v>1.14371391169265</v>
+        <v>0.70850453736094099</v>
       </c>
       <c r="J32" s="0">
-        <v>1.3791895525062401</v>
+        <v>1.3792145509171001</v>
       </c>
       <c r="K32" s="0">
-        <v>-0.14525462204609901</v>
+        <v>-0.63302878173904908</v>
       </c>
       <c r="L32" s="0">
-        <v>0.73422755061892497</v>
+        <v>-0.37818509647054099</v>
       </c>
       <c r="M32" s="0">
-        <v>-0.89878667589734107</v>
+        <v>-0.46357974098034799</v>
       </c>
       <c r="N32" s="0">
         <v>0</v>
@@ -1532,40 +1532,40 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>5.5678439377624498e-09</v>
+        <v>5.5681794720542704e-09</v>
       </c>
       <c r="C33" s="0">
-        <v>0.25058862038316498</v>
+        <v>0.73467537468326705</v>
       </c>
       <c r="D33" s="0">
-        <v>2.1928237586102401</v>
+        <v>2.1928234322513598</v>
       </c>
       <c r="E33" s="0">
-        <v>-0.54677235615011299</v>
+        <v>8.8947571661119395e-08</v>
       </c>
       <c r="F33" s="0">
-        <v>-0.65986145825435805</v>
+        <v>0.73857644968195602</v>
       </c>
       <c r="G33" s="0">
-        <v>1.7218797547270099</v>
+        <v>2.1928237724165398</v>
       </c>
       <c r="H33" s="0">
-        <v>-0.16016323204445501</v>
+        <v>1.04700814361281e-07</v>
       </c>
       <c r="I33" s="0">
-        <v>-2.10086979678848</v>
+        <v>0.75187926470157995</v>
       </c>
       <c r="J33" s="0">
-        <v>1.64382817041629</v>
+        <v>2.1928242357837502</v>
       </c>
       <c r="K33" s="0">
-        <v>-0.25058861481532102</v>
+        <v>-0.73467536911508757</v>
       </c>
       <c r="L33" s="0">
-        <v>0.11308910210424505</v>
+        <v>-0.73857636073438437</v>
       </c>
       <c r="M33" s="0">
-        <v>1.9407065647440249</v>
+        <v>-0.7518791600007656</v>
       </c>
       <c r="N33" s="0">
         <v>0</v>
@@ -1576,40 +1576,40 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>1.7706298528793101e-07</v>
+        <v>1.7706303409907e-07</v>
       </c>
       <c r="C34" s="0">
-        <v>0.25592838837093002</v>
+        <v>0.75802336139451698</v>
       </c>
       <c r="D34" s="0">
-        <v>0.47856267436615602</v>
+        <v>0.47856272134223499</v>
       </c>
       <c r="E34" s="0">
-        <v>-1.24304516452808</v>
+        <v>4.5429733210893803e-09</v>
       </c>
       <c r="F34" s="0">
-        <v>1.0392629129912201</v>
+        <v>0.66662034203666598</v>
       </c>
       <c r="G34" s="0">
-        <v>0.25974633854659701</v>
+        <v>0.47856249889928798</v>
       </c>
       <c r="H34" s="0">
-        <v>-0.167490357085331</v>
+        <v>2.62002396835154e-07</v>
       </c>
       <c r="I34" s="0">
-        <v>0.050389406733392601</v>
+        <v>0.61402362555408296</v>
       </c>
       <c r="J34" s="0">
-        <v>0.30986648012745699</v>
+        <v>0.47856280011172703</v>
       </c>
       <c r="K34" s="0">
-        <v>-0.25592821130794474</v>
+        <v>-0.75802318433148286</v>
       </c>
       <c r="L34" s="0">
-        <v>-2.2823080775192999</v>
+        <v>-0.66662033749369265</v>
       </c>
       <c r="M34" s="0">
-        <v>-0.21787976381872359</v>
+        <v>-0.61402336355168607</v>
       </c>
       <c r="N34" s="0">
         <v>1</v>
@@ -1620,40 +1620,40 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>8.0499325327056702e-09</v>
+        <v>8.0515217379711202e-09</v>
       </c>
       <c r="C35" s="0">
-        <v>0.25438055359004202</v>
+        <v>0.65968473881331202</v>
       </c>
       <c r="D35" s="0">
-        <v>2.8324904346122999</v>
+        <v>2.8324889353069298</v>
       </c>
       <c r="E35" s="0">
-        <v>-0.220365317397862</v>
+        <v>1.9666411775809002e-08</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.62215593138553</v>
+        <v>0.84524358858412396</v>
       </c>
       <c r="G35" s="0">
-        <v>2.44708423172735</v>
+        <v>2.83249048111225</v>
       </c>
       <c r="H35" s="0">
-        <v>-0.049367842359306802</v>
+        <v>1.5935477795107599e-07</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.9567775525284601</v>
+        <v>0.79741938296784798</v>
       </c>
       <c r="J35" s="0">
-        <v>2.5925592055989202</v>
+        <v>2.8324913616840299</v>
       </c>
       <c r="K35" s="0">
-        <v>-0.25438054554010947</v>
+        <v>-0.65968473076179024</v>
       </c>
       <c r="L35" s="0">
-        <v>1.4017906139876681</v>
+        <v>-0.84524356891771224</v>
       </c>
       <c r="M35" s="0">
-        <v>1.9074097101691532</v>
+        <v>-0.79741922361307005</v>
       </c>
       <c r="N35" s="0">
         <v>1</v>
@@ -1664,40 +1664,40 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>0.0033251086752804902</v>
+        <v>0.0031034864138280902</v>
       </c>
       <c r="C36" s="0">
-        <v>0.24999285332086599</v>
+        <v>0.74997020587174701</v>
       </c>
       <c r="D36" s="0">
-        <v>20.065993956514099</v>
+        <v>21.498918438258698</v>
       </c>
       <c r="E36" s="0">
-        <v>0.0022356488111253299</v>
+        <v>0.0032870077778077598</v>
       </c>
       <c r="F36" s="0">
-        <v>-13.607543139745699</v>
+        <v>0.75214160445786704</v>
       </c>
       <c r="G36" s="0">
-        <v>29.951064798418599</v>
+        <v>20.3711645690741</v>
       </c>
       <c r="H36" s="0">
-        <v>9.2857911101512102e-05</v>
+        <v>0.00067652748112705802</v>
       </c>
       <c r="I36" s="0">
-        <v>-822.27325479803199</v>
+        <v>0.75</v>
       </c>
       <c r="J36" s="0">
-        <v>715.91925320766597</v>
+        <v>98.1717366098799</v>
       </c>
       <c r="K36" s="0">
-        <v>-0.2466677446455855</v>
+        <v>-0.74686671945791894</v>
       </c>
       <c r="L36" s="0">
-        <v>13.609778788556824</v>
+        <v>-0.74885459668005927</v>
       </c>
       <c r="M36" s="0">
-        <v>822.2733476559431</v>
+        <v>-0.74932347251887299</v>
       </c>
       <c r="N36" s="0">
         <v>1</v>
@@ -1708,40 +1708,40 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>3.7906137498806196e-09</v>
+        <v>8.39385372507619e-10</v>
       </c>
       <c r="C37" s="0">
-        <v>0.24999948377746301</v>
+        <v>0.75012955475814902</v>
       </c>
       <c r="D37" s="0">
-        <v>20.0969886543248</v>
+        <v>22.612478562726</v>
       </c>
       <c r="E37" s="0">
-        <v>-0.0221040678203832</v>
+        <v>6.0186768631458298e-08</v>
       </c>
       <c r="F37" s="0">
-        <v>-31.170969181968498</v>
+        <v>0.79143636676660001</v>
       </c>
       <c r="G37" s="0">
-        <v>28.2220789012663</v>
+        <v>18.989409161877301</v>
       </c>
       <c r="H37" s="0">
-        <v>-0.00086739327474275995</v>
+        <v>1.11527740629e-08</v>
       </c>
       <c r="I37" s="0">
-        <v>-1268.34212790835</v>
+        <v>0.74998094704575302</v>
       </c>
       <c r="J37" s="0">
-        <v>715.55544276455305</v>
+        <v>20.4936694088357</v>
       </c>
       <c r="K37" s="0">
-        <v>-0.24999947998684927</v>
+        <v>-0.75012955391876368</v>
       </c>
       <c r="L37" s="0">
-        <v>31.148865114148116</v>
+        <v>-0.79143630657983133</v>
       </c>
       <c r="M37" s="0">
-        <v>1268.3412605150752</v>
+        <v>-0.74998093589297898</v>
       </c>
       <c r="N37" s="0">
         <v>1</v>
@@ -1752,40 +1752,40 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C38" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D38" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E38" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F38" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G38" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H38" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I38" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J38" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K38" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L38" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M38" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N38" s="0">
         <v>1</v>
@@ -1796,40 +1796,40 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C39" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D39" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E39" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F39" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G39" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H39" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I39" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J39" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K39" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L39" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M39" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N39" s="0">
         <v>1</v>
@@ -1840,40 +1840,40 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>1.04638217529286e-08</v>
+        <v>1.0463903410220701e-08</v>
       </c>
       <c r="C40" s="0">
-        <v>0.25198342239128602</v>
+        <v>0.67450956915304705</v>
       </c>
       <c r="D40" s="0">
-        <v>1.39990526201518</v>
+        <v>1.3999050347720701</v>
       </c>
       <c r="E40" s="0">
-        <v>-0.45720818522835799</v>
+        <v>1.5857475420595901e-07</v>
       </c>
       <c r="F40" s="0">
-        <v>-0.27877219866875003</v>
+        <v>0.62678044802890698</v>
       </c>
       <c r="G40" s="0">
-        <v>1.0903278761787301</v>
+        <v>1.3999058735683401</v>
       </c>
       <c r="H40" s="0">
-        <v>-0.078147455298525501</v>
+        <v>2.29485784295206e-07</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.657921638053101</v>
+        <v>0.66104676999904</v>
       </c>
       <c r="J40" s="0">
-        <v>1.19279020953423</v>
+        <v>1.3999066569207801</v>
       </c>
       <c r="K40" s="0">
-        <v>-0.25198341192746426</v>
+        <v>-0.67450955868914364</v>
       </c>
       <c r="L40" s="0">
-        <v>-0.17843598655960796</v>
+        <v>-0.62678028945415276</v>
       </c>
       <c r="M40" s="0">
-        <v>0.57977418275457548</v>
+        <v>-0.66104654051325573</v>
       </c>
       <c r="N40" s="0">
         <v>1</v>
@@ -1884,40 +1884,40 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>0.0024462448346211701</v>
+        <v>0.0024461314753308401</v>
       </c>
       <c r="C41" s="0">
-        <v>0.24996454550407499</v>
+        <v>0.75090903898959505</v>
       </c>
       <c r="D41" s="0">
-        <v>2.20987503892857</v>
+        <v>2.2098743420536699</v>
       </c>
       <c r="E41" s="0">
-        <v>-0.00621707513875397</v>
+        <v>7.1833438896393099e-07</v>
       </c>
       <c r="F41" s="0">
-        <v>-0.32516405030747902</v>
+        <v>0.73932058957031099</v>
       </c>
       <c r="G41" s="0">
-        <v>2.1790312306694699</v>
+        <v>2.19282524052193</v>
       </c>
       <c r="H41" s="0">
-        <v>0.00335734583382442</v>
+        <v>0.0033597676558066898</v>
       </c>
       <c r="I41" s="0">
-        <v>-2.00855756550455</v>
+        <v>0.72089419224977203</v>
       </c>
       <c r="J41" s="0">
-        <v>2.2098129029334102</v>
+        <v>2.2098196286512399</v>
       </c>
       <c r="K41" s="0">
-        <v>-0.24751830066945382</v>
+        <v>-0.74846290751426425</v>
       </c>
       <c r="L41" s="0">
-        <v>0.31894697516872506</v>
+        <v>-0.73931987123592202</v>
       </c>
       <c r="M41" s="0">
-        <v>2.0119149113383745</v>
+        <v>-0.71753442459396533</v>
       </c>
       <c r="N41" s="0">
         <v>1</v>
@@ -1928,40 +1928,40 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>3.61489718599338e-09</v>
+        <v>1.09990877007998e-07</v>
       </c>
       <c r="C42" s="0">
-        <v>0.25801954435270902</v>
+        <v>0.74994906264785599</v>
       </c>
       <c r="D42" s="0">
-        <v>21.084254763068099</v>
+        <v>17.3182842108925</v>
       </c>
       <c r="E42" s="0">
-        <v>-0.022096522493608699</v>
+        <v>6.0007872358033206e-08</v>
       </c>
       <c r="F42" s="0">
-        <v>-31.181397551700801</v>
+        <v>0.79075497118681104</v>
       </c>
       <c r="G42" s="0">
-        <v>28.2317146091567</v>
+        <v>19.045860740660501</v>
       </c>
       <c r="H42" s="0">
-        <v>-0.00086739327474275995</v>
+        <v>6.0804612864223696e-08</v>
       </c>
       <c r="I42" s="0">
-        <v>-1268.34212790835</v>
+        <v>0.75029126022405901</v>
       </c>
       <c r="J42" s="0">
-        <v>715.55544276455305</v>
+        <v>18.799442014161301</v>
       </c>
       <c r="K42" s="0">
-        <v>-0.25801954073781186</v>
+        <v>-0.74994895265697903</v>
       </c>
       <c r="L42" s="0">
-        <v>31.159301029207192</v>
+        <v>-0.7907549111789387</v>
       </c>
       <c r="M42" s="0">
-        <v>1268.3412605150752</v>
+        <v>-0.75029119941944611</v>
       </c>
       <c r="N42" s="0">
         <v>1</v>
@@ -1972,40 +1972,40 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>0.29867159825934803</v>
+        <v>1.4999962353456</v>
       </c>
       <c r="C43" s="0">
-        <v>0.240414043175567</v>
+        <v>0.75390076184931798</v>
       </c>
       <c r="D43" s="0">
-        <v>5.09868070635178e-09</v>
+        <v>0.015410186553960399</v>
       </c>
       <c r="E43" s="0">
-        <v>0.109087960513708</v>
+        <v>1.06775597147949</v>
       </c>
       <c r="F43" s="0">
-        <v>0.39921650206879</v>
+        <v>0.75030793203387802</v>
       </c>
       <c r="G43" s="0">
-        <v>-0.52321561840128805</v>
+        <v>2.1850577141583201e-08</v>
       </c>
       <c r="H43" s="0">
-        <v>0.17600367419191401</v>
+        <v>0.76994978595419905</v>
       </c>
       <c r="I43" s="0">
-        <v>0.33635998816992901</v>
+        <v>0.75177178608673101</v>
       </c>
       <c r="J43" s="0">
-        <v>-0.63455234538396099</v>
+        <v>6.4671182375686094e-08</v>
       </c>
       <c r="K43" s="0">
-        <v>0.058257555083781026</v>
+        <v>0.74609547349628202</v>
       </c>
       <c r="L43" s="0">
-        <v>-0.290128541555082</v>
+        <v>0.31744803944561195</v>
       </c>
       <c r="M43" s="0">
-        <v>-0.160356313978015</v>
+        <v>0.018177999867468042</v>
       </c>
       <c r="N43" s="0">
         <v>1</v>
@@ -2016,40 +2016,40 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C44" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D44" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E44" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F44" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G44" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H44" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I44" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J44" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K44" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L44" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M44" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N44" s="0">
         <v>1</v>
@@ -2060,40 +2060,40 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>1.2845226512681701e-08</v>
+        <v>1.2846047612015099e-08</v>
       </c>
       <c r="C45" s="0">
-        <v>0.25236599028614598</v>
+        <v>0.677534329099584</v>
       </c>
       <c r="D45" s="0">
-        <v>1.2487144365001099</v>
+        <v>1.24871451666386</v>
       </c>
       <c r="E45" s="0">
-        <v>-0.31815613005437998</v>
+        <v>2.2958600238990701e-07</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.227920710677323</v>
+        <v>0.64082026056421104</v>
       </c>
       <c r="G45" s="0">
-        <v>1.02385313532921</v>
+        <v>1.2487145747181101</v>
       </c>
       <c r="H45" s="0">
-        <v>-0.0458141393867195</v>
+        <v>6.4601878501100497e-07</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.33044824534121398</v>
+        <v>0.77027278025660795</v>
       </c>
       <c r="J45" s="0">
-        <v>1.1305984130454101</v>
+        <v>1.2487161250052501</v>
       </c>
       <c r="K45" s="0">
-        <v>-0.25236597744091949</v>
+        <v>-0.67753431625353644</v>
       </c>
       <c r="L45" s="0">
-        <v>-0.09023541937705698</v>
+        <v>-0.64082003097820861</v>
       </c>
       <c r="M45" s="0">
-        <v>0.28463410595449445</v>
+        <v>-0.77027213423782293</v>
       </c>
       <c r="N45" s="0">
         <v>1</v>
@@ -2104,40 +2104,40 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>2.4722031572600098e-07</v>
+        <v>2.4722038736762902e-07</v>
       </c>
       <c r="C46" s="0">
-        <v>0.25012806836537199</v>
+        <v>0.75054994683329801</v>
       </c>
       <c r="D46" s="0">
-        <v>0.202309941233977</v>
+        <v>0.20230991985427599</v>
       </c>
       <c r="E46" s="0">
-        <v>-432086945.89044499</v>
+        <v>1.97850379613519e-07</v>
       </c>
       <c r="F46" s="0">
-        <v>243339635.46867001</v>
+        <v>0.75037628927855604</v>
       </c>
       <c r="G46" s="0">
-        <v>7.3191714202648597e-10</v>
+        <v>0.20231000649238801</v>
       </c>
       <c r="H46" s="0">
-        <v>-0.24981025332123</v>
+        <v>2.3263275792609498e-08</v>
       </c>
       <c r="I46" s="0">
-        <v>0.47494733468533001</v>
+        <v>0.74809599945030603</v>
       </c>
       <c r="J46" s="0">
-        <v>0.010906740083152599</v>
+        <v>0.20230998715880799</v>
       </c>
       <c r="K46" s="0">
-        <v>-0.25012782114505627</v>
+        <v>-0.75054969961291063</v>
       </c>
       <c r="L46" s="0">
-        <v>-675426581.359115</v>
+        <v>-0.75037609142817641</v>
       </c>
       <c r="M46" s="0">
-        <v>-0.72475758800655998</v>
+        <v>-0.74809597618703028</v>
       </c>
       <c r="N46" s="0">
         <v>1</v>
@@ -2148,40 +2148,40 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C47" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D47" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E47" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F47" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G47" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H47" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I47" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J47" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K47" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L47" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M47" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N47" s="0">
         <v>1</v>
@@ -2192,40 +2192,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>4.5661682538769798e-08</v>
+        <v>9.1331183262020207e-09</v>
       </c>
       <c r="C48" s="0">
-        <v>0.251163565129221</v>
+        <v>0.70840421019314903</v>
       </c>
       <c r="D48" s="0">
-        <v>1.58740110396944</v>
+        <v>1.58740093757249</v>
       </c>
       <c r="E48" s="0">
-        <v>-0.29408616830217499</v>
+        <v>1.7504967430341099e-07</v>
       </c>
       <c r="F48" s="0">
-        <v>-0.341643788475961</v>
+        <v>0.652666466661739</v>
       </c>
       <c r="G48" s="0">
-        <v>1.3195356851153801</v>
+        <v>1.5874010809394601</v>
       </c>
       <c r="H48" s="0">
-        <v>-0.175809758556049</v>
+        <v>5.1646661837578096e-07</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.21335383953562</v>
+        <v>0.58568387327776605</v>
       </c>
       <c r="J48" s="0">
-        <v>1.14928307598715</v>
+        <v>1.5874034028722399</v>
       </c>
       <c r="K48" s="0">
-        <v>-0.25116351946753845</v>
+        <v>-0.70840420106003066</v>
       </c>
       <c r="L48" s="0">
-        <v>0.047557620173786008</v>
+        <v>-0.65266629161206469</v>
       </c>
       <c r="M48" s="0">
-        <v>1.0375440809795711</v>
+        <v>-0.58568335681114769</v>
       </c>
       <c r="N48" s="0">
         <v>1</v>
@@ -2236,40 +2236,40 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>1.0575977198304401e-09</v>
+        <v>3.8819287800219601e-08</v>
       </c>
       <c r="C49" s="0">
-        <v>0.29693646778867</v>
+        <v>0.68284160149118101</v>
       </c>
       <c r="D49" s="0">
-        <v>29.253680025527501</v>
+        <v>19.087334018985398</v>
       </c>
       <c r="E49" s="0">
-        <v>-0.0131630686981515</v>
+        <v>8.7719616042634997e-08</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.87201242011165003</v>
+        <v>0.62084143725015695</v>
       </c>
       <c r="G49" s="0">
-        <v>28.694252711040001</v>
+        <v>18.240726622558199</v>
       </c>
       <c r="H49" s="0">
-        <v>-0.00051562989337764896</v>
+        <v>8.4564190329879698e-08</v>
       </c>
       <c r="I49" s="0">
-        <v>-679.48246307440104</v>
+        <v>0.74987243886367305</v>
       </c>
       <c r="J49" s="0">
-        <v>720.59499250742203</v>
+        <v>18.929759622005101</v>
       </c>
       <c r="K49" s="0">
-        <v>-0.29693646673107227</v>
+        <v>-0.68284156267189322</v>
       </c>
       <c r="L49" s="0">
-        <v>0.8588493514134985</v>
+        <v>-0.62084134953054093</v>
       </c>
       <c r="M49" s="0">
-        <v>679.48194744450768</v>
+        <v>-0.74987235429948274</v>
       </c>
       <c r="N49" s="0">
         <v>1</v>
@@ -2280,40 +2280,40 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>1.2562614392099701e-09</v>
+        <v>1.2558653264463e-07</v>
       </c>
       <c r="C50" s="0">
-        <v>0.255485621756602</v>
+        <v>0.65945751539883402</v>
       </c>
       <c r="D50" s="0">
-        <v>0.67399638505523995</v>
+        <v>0.67399661110910902</v>
       </c>
       <c r="E50" s="0">
-        <v>-0.61308446036347597</v>
+        <v>7.5585919772747294e-08</v>
       </c>
       <c r="F50" s="0">
-        <v>0.67280798610463699</v>
+        <v>0.695069893338363</v>
       </c>
       <c r="G50" s="0">
-        <v>0.475581716495384</v>
+        <v>0.67399667306844702</v>
       </c>
       <c r="H50" s="0">
-        <v>0.050894172753048</v>
+        <v>0.050885461236686698</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.40717388763809698</v>
+        <v>0.75008021460101204</v>
       </c>
       <c r="J50" s="0">
-        <v>0.74335439695234695</v>
+        <v>0.74336328505582605</v>
       </c>
       <c r="K50" s="0">
-        <v>-0.25548562050034057</v>
+        <v>-0.6594573898123014</v>
       </c>
       <c r="L50" s="0">
-        <v>-1.285892446468113</v>
+        <v>-0.69506981775244325</v>
       </c>
       <c r="M50" s="0">
-        <v>0.458068060391145</v>
+        <v>-0.69919475336432535</v>
       </c>
       <c r="N50" s="0">
         <v>0</v>
@@ -2324,40 +2324,40 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>1.0544840840445e-07</v>
+        <v>1.0544838163066201e-07</v>
       </c>
       <c r="C51" s="0">
-        <v>0.25097099639932802</v>
+        <v>0.67900401414739597</v>
       </c>
       <c r="D51" s="0">
-        <v>0.67399652325481796</v>
+        <v>0.67399650159835001</v>
       </c>
       <c r="E51" s="0">
-        <v>0.0061829697317560802</v>
+        <v>0.0061853257349112198</v>
       </c>
       <c r="F51" s="0">
-        <v>-0.53808007708400296</v>
+        <v>0.77572954430273899</v>
       </c>
       <c r="G51" s="0">
-        <v>0.67729250034205302</v>
+        <v>0.67728736890177499</v>
       </c>
       <c r="H51" s="0">
-        <v>-0.0199439657617826</v>
+        <v>1.4390931254395499e-07</v>
       </c>
       <c r="I51" s="0">
-        <v>0.66525142488179201</v>
+        <v>0.75770532762757403</v>
       </c>
       <c r="J51" s="0">
-        <v>0.64622138651696004</v>
+        <v>0.67399657616001296</v>
       </c>
       <c r="K51" s="0">
-        <v>-0.25097089095091962</v>
+        <v>-0.67900390869901439</v>
       </c>
       <c r="L51" s="0">
-        <v>0.54426304681575899</v>
+        <v>-0.76954421856782773</v>
       </c>
       <c r="M51" s="0">
-        <v>-0.6851953906435746</v>
+        <v>-0.75770518371826145</v>
       </c>
       <c r="N51" s="0">
         <v>0</v>
@@ -2368,40 +2368,40 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C52" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D52" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E52" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F52" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G52" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H52" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I52" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J52" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K52" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L52" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M52" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N52" s="0">
         <v>0</v>
@@ -2412,40 +2412,40 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C53" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D53" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E53" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F53" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G53" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H53" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I53" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J53" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K53" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L53" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M53" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N53" s="0">
         <v>0</v>
@@ -2456,40 +2456,40 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>4.9804066928760496e-09</v>
+        <v>4.9620165998471804e-09</v>
       </c>
       <c r="C54" s="0">
-        <v>0.250116642212667</v>
+        <v>0.72870471506568701</v>
       </c>
       <c r="D54" s="0">
-        <v>2.1928084083836898</v>
+        <v>2.1928236668188199</v>
       </c>
       <c r="E54" s="0">
-        <v>-22.571498269611499</v>
+        <v>7.4430231810246799e-08</v>
       </c>
       <c r="F54" s="0">
-        <v>9.10776545429799</v>
+        <v>0.73743585143104995</v>
       </c>
       <c r="G54" s="0">
-        <v>1.5874009572813801</v>
+        <v>2.1928238038110699</v>
       </c>
       <c r="H54" s="0">
-        <v>-0.249999999696848</v>
+        <v>6.1826449159618203e-10</v>
       </c>
       <c r="I54" s="0">
-        <v>-2.3951560689293498</v>
+        <v>0.695476655678956</v>
       </c>
       <c r="J54" s="0">
-        <v>1.9352020854013201</v>
+        <v>2.1928236656004301</v>
       </c>
       <c r="K54" s="0">
-        <v>-0.2501166372322603</v>
+        <v>-0.72870471010367044</v>
       </c>
       <c r="L54" s="0">
-        <v>-31.679263723909489</v>
+        <v>-0.73743577700081819</v>
       </c>
       <c r="M54" s="0">
-        <v>2.145156069232502</v>
+        <v>-0.69547665506069156</v>
       </c>
       <c r="N54" s="0">
         <v>0</v>
@@ -2500,40 +2500,40 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>0.017213853750087799</v>
+        <v>0.0172138555377357</v>
       </c>
       <c r="C55" s="0">
-        <v>0.24963538861616999</v>
+        <v>0.74973470242060802</v>
       </c>
       <c r="D55" s="0">
-        <v>2.3362347133660402</v>
+        <v>2.33623495507964</v>
       </c>
       <c r="E55" s="0">
-        <v>0.0404177668031706</v>
+        <v>0.040416541432692299</v>
       </c>
       <c r="F55" s="0">
-        <v>0.084365490552431005</v>
+        <v>0.73417772102683398</v>
       </c>
       <c r="G55" s="0">
-        <v>2.2957707718113798</v>
+        <v>2.2957797323201499</v>
       </c>
       <c r="H55" s="0">
-        <v>0.040333123929303299</v>
+        <v>0.040336149255302697</v>
       </c>
       <c r="I55" s="0">
-        <v>-2.1834063729317998</v>
+        <v>0.75850505147032798</v>
       </c>
       <c r="J55" s="0">
-        <v>2.4266621098691501</v>
+        <v>2.4267090014843</v>
       </c>
       <c r="K55" s="0">
-        <v>-0.23242153486608219</v>
+        <v>-0.73252084688287233</v>
       </c>
       <c r="L55" s="0">
-        <v>-0.043947723749260405</v>
+        <v>-0.69376117959414163</v>
       </c>
       <c r="M55" s="0">
-        <v>2.2237394968611031</v>
+        <v>-0.71816890221502527</v>
       </c>
       <c r="N55" s="0">
         <v>0</v>
@@ -2544,40 +2544,40 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>4.7803657866101201e-09</v>
+        <v>4.7804130493386796e-09</v>
       </c>
       <c r="C56" s="0">
-        <v>0.25407623889458097</v>
+        <v>0.71911294019473104</v>
       </c>
       <c r="D56" s="0">
-        <v>2.8324904563478701</v>
+        <v>2.83249033940761</v>
       </c>
       <c r="E56" s="0">
-        <v>-0.37886909388810702</v>
+        <v>1.5381992196819599e-08</v>
       </c>
       <c r="F56" s="0">
-        <v>-1.64022836874319</v>
+        <v>0.83798127457514604</v>
       </c>
       <c r="G56" s="0">
-        <v>2.3422651237254399</v>
+        <v>2.8324902885808299</v>
       </c>
       <c r="H56" s="0">
-        <v>-0.15272552386024499</v>
+        <v>8.3750140992624501e-08</v>
       </c>
       <c r="I56" s="0">
-        <v>-3.1550074727581099</v>
+        <v>0.84896061068656004</v>
       </c>
       <c r="J56" s="0">
-        <v>2.2279134693049301</v>
+        <v>2.8324907356029301</v>
       </c>
       <c r="K56" s="0">
-        <v>-0.2540762341142152</v>
+        <v>-0.71911293541431798</v>
       </c>
       <c r="L56" s="0">
-        <v>1.261359274855083</v>
+        <v>-0.8379812591931538</v>
       </c>
       <c r="M56" s="0">
-        <v>3.0022819488978647</v>
+        <v>-0.84896052693641899</v>
       </c>
       <c r="N56" s="0">
         <v>0</v>
@@ -2588,40 +2588,40 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>0.041159902673175798</v>
+        <v>0.041159798449173397</v>
       </c>
       <c r="C57" s="0">
-        <v>0.24975737417031099</v>
+        <v>0.75777304517358002</v>
       </c>
       <c r="D57" s="0">
-        <v>0.40124772959855298</v>
+        <v>0.40124757159693902</v>
       </c>
       <c r="E57" s="0">
-        <v>0.022784368232823999</v>
+        <v>0.022795476873209101</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.043176493670030999</v>
+        <v>0.75538651493068398</v>
       </c>
       <c r="G57" s="0">
-        <v>0.36929741241638098</v>
+        <v>0.36930408392986802</v>
       </c>
       <c r="H57" s="0">
-        <v>0.021881106895225998</v>
+        <v>0.021887900233642999</v>
       </c>
       <c r="I57" s="0">
-        <v>0.00055151142339663001</v>
+        <v>0.77097434270367604</v>
       </c>
       <c r="J57" s="0">
-        <v>0.37867920133585597</v>
+        <v>0.37869008043788899</v>
       </c>
       <c r="K57" s="0">
-        <v>-0.2085974714971352</v>
+        <v>-0.71661324672440663</v>
       </c>
       <c r="L57" s="0">
-        <v>0.065960861902854995</v>
+        <v>-0.73259103805747483</v>
       </c>
       <c r="M57" s="0">
-        <v>0.021329595471829367</v>
+        <v>-0.74908644247003309</v>
       </c>
       <c r="N57" s="0">
         <v>0</v>
@@ -2632,40 +2632,40 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C58" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D58" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E58" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F58" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G58" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H58" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I58" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J58" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K58" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L58" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M58" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N58" s="0">
         <v>0</v>
@@ -2676,40 +2676,40 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C59" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D59" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E59" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F59" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G59" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H59" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I59" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J59" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K59" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L59" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M59" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N59" s="0">
         <v>0</v>
@@ -2720,40 +2720,40 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C60" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D60" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E60" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F60" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G60" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H60" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I60" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J60" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K60" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L60" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M60" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N60" s="0">
         <v>0</v>
@@ -2764,40 +2764,40 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C61" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D61" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E61" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F61" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G61" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H61" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I61" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J61" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K61" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L61" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M61" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N61" s="0">
         <v>0</v>
@@ -2808,40 +2808,40 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C62" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D62" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E62" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F62" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G62" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H62" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I62" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J62" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K62" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L62" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M62" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N62" s="0">
         <v>0</v>
@@ -2852,40 +2852,40 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C63" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D63" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E63" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F63" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G63" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H63" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I63" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J63" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K63" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L63" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M63" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N63" s="0">
         <v>0</v>
@@ -2896,40 +2896,40 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>5.0223267586833897e-08</v>
+        <v>1.00433002353221e-08</v>
       </c>
       <c r="C64" s="0">
-        <v>0.179593902170259</v>
+        <v>0.53962603481100102</v>
       </c>
       <c r="D64" s="0">
-        <v>0.74775868025521797</v>
+        <v>0.74775899176557703</v>
       </c>
       <c r="E64" s="0">
-        <v>-2.2764660259341101</v>
+        <v>1.7726936265894699e-07</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.1853320694154399</v>
+        <v>0.620634581256018</v>
       </c>
       <c r="G64" s="0">
-        <v>0.34401587904520903</v>
+        <v>0.74775895158734995</v>
       </c>
       <c r="H64" s="0">
-        <v>-0.249999485657207</v>
+        <v>2.34216527096349e-08</v>
       </c>
       <c r="I64" s="0">
-        <v>0.025777101078460301</v>
+        <v>0.61587988763706103</v>
       </c>
       <c r="J64" s="0">
-        <v>0.44746632243551399</v>
+        <v>0.74775872574923696</v>
       </c>
       <c r="K64" s="0">
-        <v>-0.1795938519469914</v>
+        <v>-0.53962602476770083</v>
       </c>
       <c r="L64" s="0">
-        <v>-1.0911339565186702</v>
+        <v>-0.62063440398665537</v>
       </c>
       <c r="M64" s="0">
-        <v>-0.2757765867356673</v>
+        <v>-0.6158798642154083</v>
       </c>
       <c r="N64" s="0">
         <v>0</v>
@@ -2940,40 +2940,40 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>5.7431435137855596e-09</v>
+        <v>5.7435166603986097e-09</v>
       </c>
       <c r="C65" s="0">
-        <v>0.25071380353503597</v>
+        <v>0.73446165631583904</v>
       </c>
       <c r="D65" s="0">
-        <v>2.1928236303868101</v>
+        <v>2.1928236799268199</v>
       </c>
       <c r="E65" s="0">
-        <v>-0.41167468703279098</v>
+        <v>9.8559392283197904e-08</v>
       </c>
       <c r="F65" s="0">
-        <v>-0.43287507244683998</v>
+        <v>0.73888067807461</v>
       </c>
       <c r="G65" s="0">
-        <v>1.77031851483276</v>
+        <v>2.1928237346811201</v>
       </c>
       <c r="H65" s="0">
-        <v>-0.19159487092311001</v>
+        <v>1.87017882938826e-08</v>
       </c>
       <c r="I65" s="0">
-        <v>-1.92800646631255</v>
+        <v>0.75190893368900502</v>
       </c>
       <c r="J65" s="0">
-        <v>1.5901352156410899</v>
+        <v>2.1928239250677999</v>
       </c>
       <c r="K65" s="0">
-        <v>-0.25071379779189246</v>
+        <v>-0.73446165057232238</v>
       </c>
       <c r="L65" s="0">
-        <v>0.021200385414049006</v>
+        <v>-0.73888057951521768</v>
       </c>
       <c r="M65" s="0">
-        <v>1.7364115953894399</v>
+        <v>-0.75190891498721668</v>
       </c>
       <c r="N65" s="0">
         <v>0</v>
